--- a/human_resources_forms/006_online_job_application_form--human_resources_forms.xlsx
+++ b/human_resources_forms/006_online_job_application_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1194,8 +1194,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'location1',_'value':_'location_1'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'location1', 'value': 'Location 1'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'location2',_'value':_'location_2'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'location2', 'value': 'Location 2'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active',_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'active', 'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'inactive',_'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'inactive', 'value': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high_school',_'value':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'high_school', 'value': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'college',_'value':_'college'}</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'college', 'value': 'College'}</t>
+          <t>College</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'person1',_'value':_'person_1'}</t>
+          <t>person_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'person1', 'value': 'Person 1'}</t>
+          <t>Person 1</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'person2',_'value':_'person_2'}</t>
+          <t>person_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'person2', 'value': 'Person 2'}</t>
+          <t>Person 2</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'person1',_'value':_'person_1'}</t>
+          <t>person_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'person1', 'value': 'Person 1'}</t>
+          <t>Person 1</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'person2',_'value':_'person_2'}</t>
+          <t>person_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'person2', 'value': 'Person 2'}</t>
+          <t>Person 2</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'person1',_'value':_'person_1'}</t>
+          <t>person_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'person1', 'value': 'Person 1'}</t>
+          <t>Person 1</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'person2',_'value':_'person_2'}</t>
+          <t>person_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'person2', 'value': 'Person 2'}</t>
+          <t>Person 2</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'person1',_'value':_'person_1'}</t>
+          <t>person_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'person1', 'value': 'Person 1'}</t>
+          <t>Person 1</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'person2',_'value':_'person_2'}</t>
+          <t>person_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'person2', 'value': 'Person 2'}</t>
+          <t>Person 2</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'pending', 'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'approved',_'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'approved', 'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'person1',_'value':_'person_1'}</t>
+          <t>person_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'person1', 'value': 'Person 1'}</t>
+          <t>Person 1</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'person_goals',_'value':_'person_2'}</t>
+          <t>person_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'person_goals', 'value': 'Person 2'}</t>
+          <t>Person 2</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'person1',_'value':_'person_1'}</t>
+          <t>person_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'person1', 'value': 'Person 1'}</t>
+          <t>Person 1</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'person_goals',_'value':_'person_2'}</t>
+          <t>person_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'person_goals', 'value': 'Person 2'}</t>
+          <t>Person 2</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'person1',_'value':_'person_1'}</t>
+          <t>person_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'person1', 'value': 'Person 1'}</t>
+          <t>Person 1</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'person_goals',_'value':_'person_2'}</t>
+          <t>person_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'person_goals', 'value': 'Person 2'}</t>
+          <t>Person 2</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'person1',_'value':_'person_1'}</t>
+          <t>person_1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'person1', 'value': 'Person 1'}</t>
+          <t>Person 1</t>
         </is>
       </c>
     </row>
@@ -1614,12 +1614,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'person_goals',_'value':_'person_2'}</t>
+          <t>person_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'person_goals', 'value': 'Person 2'}</t>
+          <t>Person 2</t>
         </is>
       </c>
     </row>
@@ -1631,12 +1631,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'person1',_'value':_'person_1'}</t>
+          <t>person_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'person1', 'value': 'Person 1'}</t>
+          <t>Person 1</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'person_goals',_'value':_'person_2'}</t>
+          <t>person_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'person_goals', 'value': 'Person 2'}</t>
+          <t>Person 2</t>
         </is>
       </c>
     </row>
@@ -1665,12 +1665,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'person1',_'value':_'person_1'}</t>
+          <t>person_1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'person1', 'value': 'Person 1'}</t>
+          <t>Person 1</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'person_goals',_'value':_'person_2'}</t>
+          <t>person_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'person_goals', 'value': 'Person 2'}</t>
+          <t>Person 2</t>
         </is>
       </c>
     </row>
@@ -1699,12 +1699,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'pending', 'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1716,12 +1716,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'approved',_'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'approved', 'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'person1',_'value':_'person_1'}</t>
+          <t>person_1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'person1', 'value': 'Person 1'}</t>
+          <t>Person 1</t>
         </is>
       </c>
     </row>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'person_goals',_'value':_'person_2'}</t>
+          <t>person_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'person_goals', 'value': 'Person 2'}</t>
+          <t>Person 2</t>
         </is>
       </c>
     </row>
